--- a/backtest/results_us100/七星美股版_实盘交易记录.xlsx
+++ b/backtest/results_us100/七星美股版_实盘交易记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="52">
   <si>
     <t>交易日期</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
   </si>
   <si>
     <t>EOG</t>
@@ -524,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -558,13 +561,13 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>143.76</v>
@@ -576,7 +579,7 @@
         <v>1.850703026003797</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -584,13 +587,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>296.92</v>
@@ -602,7 +605,7 @@
         <v>1.048568944225358</v>
       </c>
       <c r="H3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -610,13 +613,13 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>174.77</v>
@@ -628,7 +631,7 @@
         <v>0.5049917097513827</v>
       </c>
       <c r="H4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -636,13 +639,13 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5">
         <v>170.94</v>
@@ -654,7 +657,7 @@
         <v>0.5049917097513827</v>
       </c>
       <c r="H5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -662,13 +665,13 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6">
         <v>140.52</v>
@@ -680,7 +683,7 @@
         <v>1.850703026003797</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -688,13 +691,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>175.36</v>
@@ -706,7 +709,7 @@
         <v>1.290286230231872</v>
       </c>
       <c r="H7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -714,13 +717,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>126.13</v>
@@ -732,7 +735,7 @@
         <v>0.8744027938204831</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -740,13 +743,13 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9">
         <v>115.71</v>
@@ -758,7 +761,7 @@
         <v>0.5494489168637116</v>
       </c>
       <c r="H9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -766,13 +769,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>392.73</v>
@@ -784,7 +787,7 @@
         <v>0.5675635282792316</v>
       </c>
       <c r="H10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -792,13 +795,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>46.48</v>
@@ -810,7 +813,7 @@
         <v>8.156762029709951</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -818,13 +821,13 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12">
         <v>146.89</v>
@@ -836,7 +839,7 @@
         <v>6.871727331450243</v>
       </c>
       <c r="H12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -844,13 +847,13 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E13">
         <v>357.14</v>
@@ -862,7 +865,7 @@
         <v>0.5675635282792316</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -870,13 +873,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E14">
         <v>838.28</v>
@@ -888,7 +891,7 @@
         <v>4.291107478203252</v>
       </c>
       <c r="H14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -896,13 +899,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15">
         <v>286</v>
@@ -914,7 +917,7 @@
         <v>1.048568944225358</v>
       </c>
       <c r="H15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -922,13 +925,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E16">
         <v>73.09999999999999</v>
@@ -940,7 +943,7 @@
         <v>4.490398840085638</v>
       </c>
       <c r="H16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -948,13 +951,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E17">
         <v>69.37</v>
@@ -966,7 +969,7 @@
         <v>4.490398840085638</v>
       </c>
       <c r="H17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -974,13 +977,13 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E18">
         <v>135.76</v>
@@ -992,7 +995,7 @@
         <v>7.677801960298933</v>
       </c>
       <c r="H18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1000,13 +1003,13 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E19">
         <v>908.0599999999999</v>
@@ -1018,7 +1021,7 @@
         <v>4.291107478203252</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1026,13 +1029,13 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E20">
         <v>81.91</v>
@@ -1044,7 +1047,7 @@
         <v>3.650597275283464</v>
       </c>
       <c r="H20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1052,13 +1055,13 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E21">
         <v>152.61</v>
@@ -1070,7 +1073,7 @@
         <v>6.871727331450243</v>
       </c>
       <c r="H21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1078,13 +1081,13 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>917.05</v>
@@ -1096,7 +1099,7 @@
         <v>4.101054724283061</v>
       </c>
       <c r="H22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1104,13 +1107,13 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E23">
         <v>39.66</v>
@@ -1122,7 +1125,7 @@
         <v>8.156762029709951</v>
       </c>
       <c r="H23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1130,13 +1133,13 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E24">
         <v>102.89</v>
@@ -1148,7 +1151,7 @@
         <v>4.548675345807821</v>
       </c>
       <c r="H24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1156,13 +1159,13 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E25">
         <v>176.29</v>
@@ -1174,7 +1177,7 @@
         <v>1.290286230231872</v>
       </c>
       <c r="H25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1182,13 +1185,13 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E26">
         <v>139.32</v>
@@ -1200,7 +1203,7 @@
         <v>0.8744027938204831</v>
       </c>
       <c r="H26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1208,13 +1211,13 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E27">
         <v>125.76</v>
@@ -1226,7 +1229,7 @@
         <v>0.5494489168637116</v>
       </c>
       <c r="H27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1234,13 +1237,13 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E28">
         <v>140.45</v>
@@ -1252,7 +1255,7 @@
         <v>7.677801960298933</v>
       </c>
       <c r="H28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1260,13 +1263,13 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E29">
         <v>82.61</v>
@@ -1278,7 +1281,7 @@
         <v>3.650597275283464</v>
       </c>
       <c r="H29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1286,13 +1289,13 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E30">
         <v>860</v>
@@ -1304,7 +1307,7 @@
         <v>4.101054724283061</v>
       </c>
       <c r="H30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1312,13 +1315,13 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E31">
         <v>106.97</v>
@@ -1330,7 +1333,7 @@
         <v>4.548675345807821</v>
       </c>
       <c r="H31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1338,13 +1341,13 @@
         <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E32">
         <v>129.35</v>
@@ -1356,7 +1359,7 @@
         <v>13.60666220243627</v>
       </c>
       <c r="H32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1364,13 +1367,13 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E33">
         <v>144.25</v>
@@ -1382,7 +1385,7 @@
         <v>6.582518255184114</v>
       </c>
       <c r="H33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1390,13 +1393,13 @@
         <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E34">
         <v>123.23</v>
@@ -1408,7 +1411,7 @@
         <v>5.712362312360674</v>
       </c>
       <c r="H34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1416,13 +1419,13 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E35">
         <v>148.95</v>
@@ -1434,7 +1437,7 @@
         <v>3.492246342195308</v>
       </c>
       <c r="H35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1442,13 +1445,13 @@
         <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E36">
         <v>82.47</v>
@@ -1460,7 +1463,7 @@
         <v>2.542131667306065</v>
       </c>
       <c r="H36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1468,13 +1471,13 @@
         <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E37">
         <v>849.61</v>
@@ -1486,7 +1489,7 @@
         <v>1.638536449057692</v>
       </c>
       <c r="H37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1494,13 +1497,13 @@
         <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E38">
         <v>946.45</v>
@@ -1512,7 +1515,7 @@
         <v>1.104587343460544</v>
       </c>
       <c r="H38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1520,13 +1523,13 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E39">
         <v>872.74</v>
@@ -1538,7 +1541,7 @@
         <v>1.638536449057692</v>
       </c>
       <c r="H39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1546,13 +1549,13 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E40">
         <v>168.7</v>
@@ -1564,7 +1567,33 @@
         <v>0.5870721095223653</v>
       </c>
       <c r="H40" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" t="s">
+        <v>39</v>
+      </c>
+      <c r="E41">
+        <v>160.79</v>
+      </c>
+      <c r="F41">
+        <v>41</v>
+      </c>
+      <c r="G41">
+        <v>0.5870721095223653</v>
+      </c>
+      <c r="H41" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/backtest/results_us100/七星美股版_实盘交易记录.xlsx
+++ b/backtest/results_us100/七星美股版_实盘交易记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="59">
   <si>
     <t>交易日期</t>
   </si>
@@ -85,6 +85,21 @@
     <t>2026-09-08</t>
   </si>
   <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
     <t>EOG</t>
   </si>
   <si>
@@ -128,6 +143,12 @@
   </si>
   <si>
     <t>MU</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>ARM</t>
   </si>
   <si>
     <t>买入</t>
@@ -527,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -561,13 +582,13 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E2">
         <v>143.76</v>
@@ -579,7 +600,7 @@
         <v>1.850703026003797</v>
       </c>
       <c r="H2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -587,13 +608,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E3">
         <v>296.92</v>
@@ -605,7 +626,7 @@
         <v>1.048568944225358</v>
       </c>
       <c r="H3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -613,13 +634,13 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E4">
         <v>174.77</v>
@@ -631,7 +652,7 @@
         <v>0.5049917097513827</v>
       </c>
       <c r="H4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -639,13 +660,13 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E5">
         <v>170.94</v>
@@ -657,7 +678,7 @@
         <v>0.5049917097513827</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -665,13 +686,13 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E6">
         <v>140.52</v>
@@ -683,7 +704,7 @@
         <v>1.850703026003797</v>
       </c>
       <c r="H6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -691,13 +712,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E7">
         <v>175.36</v>
@@ -709,7 +730,7 @@
         <v>1.290286230231872</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -717,13 +738,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E8">
         <v>126.13</v>
@@ -735,7 +756,7 @@
         <v>0.8744027938204831</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -743,13 +764,13 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E9">
         <v>115.71</v>
@@ -761,7 +782,7 @@
         <v>0.5494489168637116</v>
       </c>
       <c r="H9" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -769,13 +790,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E10">
         <v>392.73</v>
@@ -787,7 +808,7 @@
         <v>0.5675635282792316</v>
       </c>
       <c r="H10" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -795,13 +816,13 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E11">
         <v>46.48</v>
@@ -813,7 +834,7 @@
         <v>8.156762029709951</v>
       </c>
       <c r="H11" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -821,13 +842,13 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E12">
         <v>146.89</v>
@@ -839,7 +860,7 @@
         <v>6.871727331450243</v>
       </c>
       <c r="H12" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -847,13 +868,13 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E13">
         <v>357.14</v>
@@ -865,7 +886,7 @@
         <v>0.5675635282792316</v>
       </c>
       <c r="H13" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -873,13 +894,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E14">
         <v>838.28</v>
@@ -891,7 +912,7 @@
         <v>4.291107478203252</v>
       </c>
       <c r="H14" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -899,13 +920,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E15">
         <v>286</v>
@@ -917,7 +938,7 @@
         <v>1.048568944225358</v>
       </c>
       <c r="H15" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -925,13 +946,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E16">
         <v>73.09999999999999</v>
@@ -943,7 +964,7 @@
         <v>4.490398840085638</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -951,13 +972,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E17">
         <v>69.37</v>
@@ -969,7 +990,7 @@
         <v>4.490398840085638</v>
       </c>
       <c r="H17" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -977,13 +998,13 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E18">
         <v>135.76</v>
@@ -995,7 +1016,7 @@
         <v>7.677801960298933</v>
       </c>
       <c r="H18" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1003,13 +1024,13 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E19">
         <v>908.0599999999999</v>
@@ -1021,7 +1042,7 @@
         <v>4.291107478203252</v>
       </c>
       <c r="H19" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1029,13 +1050,13 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E20">
         <v>81.91</v>
@@ -1047,7 +1068,7 @@
         <v>3.650597275283464</v>
       </c>
       <c r="H20" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1055,13 +1076,13 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E21">
         <v>152.61</v>
@@ -1073,7 +1094,7 @@
         <v>6.871727331450243</v>
       </c>
       <c r="H21" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1081,13 +1102,13 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E22">
         <v>917.05</v>
@@ -1099,7 +1120,7 @@
         <v>4.101054724283061</v>
       </c>
       <c r="H22" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1107,13 +1128,13 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E23">
         <v>39.66</v>
@@ -1125,7 +1146,7 @@
         <v>8.156762029709951</v>
       </c>
       <c r="H23" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1133,13 +1154,13 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E24">
         <v>102.89</v>
@@ -1151,7 +1172,7 @@
         <v>4.548675345807821</v>
       </c>
       <c r="H24" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1159,13 +1180,13 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E25">
         <v>176.29</v>
@@ -1177,7 +1198,7 @@
         <v>1.290286230231872</v>
       </c>
       <c r="H25" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1185,13 +1206,13 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E26">
         <v>139.32</v>
@@ -1203,7 +1224,7 @@
         <v>0.8744027938204831</v>
       </c>
       <c r="H26" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1211,13 +1232,13 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E27">
         <v>125.76</v>
@@ -1229,7 +1250,7 @@
         <v>0.5494489168637116</v>
       </c>
       <c r="H27" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1237,13 +1258,13 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E28">
         <v>140.45</v>
@@ -1255,7 +1276,7 @@
         <v>7.677801960298933</v>
       </c>
       <c r="H28" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1263,13 +1284,13 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E29">
         <v>82.61</v>
@@ -1281,7 +1302,7 @@
         <v>3.650597275283464</v>
       </c>
       <c r="H29" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1289,13 +1310,13 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E30">
         <v>860</v>
@@ -1307,7 +1328,7 @@
         <v>4.101054724283061</v>
       </c>
       <c r="H30" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1315,13 +1336,13 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E31">
         <v>106.97</v>
@@ -1333,7 +1354,7 @@
         <v>4.548675345807821</v>
       </c>
       <c r="H31" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1341,13 +1362,13 @@
         <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E32">
         <v>129.35</v>
@@ -1359,7 +1380,7 @@
         <v>13.60666220243627</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1367,13 +1388,13 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E33">
         <v>144.25</v>
@@ -1385,7 +1406,7 @@
         <v>6.582518255184114</v>
       </c>
       <c r="H33" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1393,13 +1414,13 @@
         <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E34">
         <v>123.23</v>
@@ -1411,7 +1432,7 @@
         <v>5.712362312360674</v>
       </c>
       <c r="H34" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1419,13 +1440,13 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E35">
         <v>148.95</v>
@@ -1437,7 +1458,7 @@
         <v>3.492246342195308</v>
       </c>
       <c r="H35" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1445,13 +1466,13 @@
         <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D36" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E36">
         <v>82.47</v>
@@ -1463,7 +1484,7 @@
         <v>2.542131667306065</v>
       </c>
       <c r="H36" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1471,13 +1492,13 @@
         <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D37" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E37">
         <v>849.61</v>
@@ -1489,7 +1510,7 @@
         <v>1.638536449057692</v>
       </c>
       <c r="H37" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1497,13 +1518,13 @@
         <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E38">
         <v>946.45</v>
@@ -1515,7 +1536,7 @@
         <v>1.104587343460544</v>
       </c>
       <c r="H38" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1523,13 +1544,13 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D39" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E39">
         <v>872.74</v>
@@ -1541,7 +1562,7 @@
         <v>1.638536449057692</v>
       </c>
       <c r="H39" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1549,13 +1570,13 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D40" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E40">
         <v>168.7</v>
@@ -1567,7 +1588,7 @@
         <v>0.5870721095223653</v>
       </c>
       <c r="H40" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1575,13 +1596,13 @@
         <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E41">
         <v>160.79</v>
@@ -1593,7 +1614,371 @@
         <v>0.5870721095223653</v>
       </c>
       <c r="H41" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42">
+        <v>127.97</v>
+      </c>
+      <c r="F42">
+        <v>54</v>
+      </c>
+      <c r="G42">
+        <v>13.60666220243627</v>
+      </c>
+      <c r="H42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>23</v>
+      </c>
+      <c r="B43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43">
+        <v>132.34</v>
+      </c>
+      <c r="F43">
+        <v>48</v>
+      </c>
+      <c r="G43">
+        <v>6.582518255184114</v>
+      </c>
+      <c r="H43" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44">
+        <v>116.69</v>
+      </c>
+      <c r="F44">
+        <v>56</v>
+      </c>
+      <c r="G44">
+        <v>5.712362312360674</v>
+      </c>
+      <c r="H44" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45">
+        <v>147.42</v>
+      </c>
+      <c r="F45">
+        <v>46</v>
+      </c>
+      <c r="G45">
+        <v>3.492246342195308</v>
+      </c>
+      <c r="H45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" t="s">
+        <v>46</v>
+      </c>
+      <c r="E46">
+        <v>76.56999999999999</v>
+      </c>
+      <c r="F46">
+        <v>84</v>
+      </c>
+      <c r="G46">
+        <v>2.542131667306065</v>
+      </c>
+      <c r="H46" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" t="s">
+        <v>42</v>
+      </c>
+      <c r="D47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47">
+        <v>1020.16</v>
+      </c>
+      <c r="F47">
+        <v>7</v>
+      </c>
+      <c r="G47">
+        <v>1.104587343460544</v>
+      </c>
+      <c r="H47" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" t="s">
+        <v>41</v>
+      </c>
+      <c r="D48" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48">
+        <v>106.33</v>
+      </c>
+      <c r="F48">
+        <v>65</v>
+      </c>
+      <c r="G48">
+        <v>5.393347801620278</v>
+      </c>
+      <c r="H48" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49">
+        <v>140.8</v>
+      </c>
+      <c r="F49">
+        <v>49</v>
+      </c>
+      <c r="G49">
+        <v>1.065587543335778</v>
+      </c>
+      <c r="H49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>24</v>
+      </c>
+      <c r="B50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50">
+        <v>151.7</v>
+      </c>
+      <c r="F50">
+        <v>46</v>
+      </c>
+      <c r="G50">
+        <v>0.5680735064005017</v>
+      </c>
+      <c r="H50" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" t="s">
         <v>43</v>
+      </c>
+      <c r="C51" t="s">
+        <v>43</v>
+      </c>
+      <c r="D51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E51">
+        <v>611.98</v>
+      </c>
+      <c r="F51">
+        <v>11</v>
+      </c>
+      <c r="G51">
+        <v>1.023925495020537</v>
+      </c>
+      <c r="H51" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" t="s">
+        <v>46</v>
+      </c>
+      <c r="E52">
+        <v>136.24</v>
+      </c>
+      <c r="F52">
+        <v>49</v>
+      </c>
+      <c r="G52">
+        <v>1.065587543335778</v>
+      </c>
+      <c r="H52" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E53">
+        <v>351.02</v>
+      </c>
+      <c r="F53">
+        <v>19</v>
+      </c>
+      <c r="G53">
+        <v>1.937990016874577</v>
+      </c>
+      <c r="H53" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>27</v>
+      </c>
+      <c r="B54" t="s">
+        <v>44</v>
+      </c>
+      <c r="C54" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" t="s">
+        <v>45</v>
+      </c>
+      <c r="E54">
+        <v>327.29</v>
+      </c>
+      <c r="F54">
+        <v>21</v>
+      </c>
+      <c r="G54">
+        <v>1.841713048985379</v>
+      </c>
+      <c r="H54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55">
+        <v>213.45</v>
+      </c>
+      <c r="F55">
+        <v>32</v>
+      </c>
+      <c r="G55">
+        <v>0.6435428559528815</v>
+      </c>
+      <c r="H55" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
